--- a/importaciones/carga masiva reclamo fraude.xlsx
+++ b/importaciones/carga masiva reclamo fraude.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7EB047-0641-4FFA-AABD-40CA1DCF91AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8558D0-9997-41FE-8EDA-E59927EBBA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>Ajustador</t>
   </si>
@@ -103,21 +103,6 @@
     <t>cob_110</t>
   </si>
   <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Result Msg</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>CL-EVR-RD</t>
   </si>
   <si>
@@ -142,15 +127,6 @@
     <t>Observación de prueba</t>
   </si>
   <si>
-    <t>4093</t>
-  </si>
-  <si>
-    <t>RV-FR-000006</t>
-  </si>
-  <si>
-    <t>8-196-813</t>
-  </si>
-  <si>
     <t>VISA</t>
   </si>
   <si>
@@ -175,15 +151,6 @@
     <t>40</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>MICHAEL DELGADO</t>
-  </si>
-  <si>
-    <t>JOSEFA MAIMONE</t>
-  </si>
-  <si>
     <t>Generales</t>
   </si>
   <si>
@@ -202,18 +169,9 @@
     <t>16/09/2026</t>
   </si>
   <si>
-    <t>4099</t>
-  </si>
-  <si>
     <t>RV-FR-000010</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>87-3944-64322</t>
-  </si>
-  <si>
     <t>master card</t>
   </si>
   <si>
@@ -235,12 +193,6 @@
     <t>panama</t>
   </si>
   <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>22/09/2026</t>
   </si>
   <si>
@@ -262,19 +214,34 @@
     <t>PANAMÁ</t>
   </si>
   <si>
-    <t>Reclamo: Ya existe el reclamo R-RV-FR-000001 (id 133) de la póliza RV-FR-000006 para el asegurado 6 JUAN CESAR ABAD ARAYA en la cobertura 40.</t>
-  </si>
-  <si>
     <t>Oficina</t>
   </si>
   <si>
     <t>Cobertura no contratada</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Reclamo: Ninguna cobertura marcada es válida: cob_109: la póliza RV-FR-000010 no tiene la cobertura 109.</t>
+    <t>329</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>20-NT-20220-14596354</t>
+  </si>
+  <si>
+    <t>08-0657-00032</t>
+  </si>
+  <si>
+    <t>08-5555-44444</t>
+  </si>
+  <si>
+    <t>08-7777-88888</t>
   </si>
 </sst>
 </file>
@@ -291,6 +258,7 @@
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -334,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -342,7 +310,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.21875" style="1" bestFit="1" customWidth="1"/>
@@ -710,12 +677,9 @@
     <col min="23" max="23" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="129.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -797,324 +761,290 @@
       <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>126</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2">
+        <v>3968</v>
+      </c>
+      <c r="L2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>126</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>3968</v>
+      </c>
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T3" t="s">
+        <v>55</v>
+      </c>
+      <c r="U3" t="s">
+        <v>56</v>
+      </c>
+      <c r="V3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>126</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4">
+        <v>3968</v>
+      </c>
+      <c r="L4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="T4" t="s">
         <v>40</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="U4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>126</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" t="s">
         <v>48</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5">
+        <v>3968</v>
+      </c>
+      <c r="L5" t="s">
         <v>49</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3" t="s">
+      <c r="M5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="Q5" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="R5" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="V5" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="3" t="s">
-        <v>84</v>
-      </c>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>

--- a/importaciones/carga masiva reclamo fraude.xlsx
+++ b/importaciones/carga masiva reclamo fraude.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8558D0-9997-41FE-8EDA-E59927EBBA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB96800-CD88-4929-AD66-E21825A5DC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,28 +220,28 @@
     <t>Cobertura no contratada</t>
   </si>
   <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>332</t>
-  </si>
-  <si>
-    <t>20-NT-20220-14596354</t>
-  </si>
-  <si>
-    <t>08-0657-00032</t>
-  </si>
-  <si>
-    <t>08-5555-44444</t>
-  </si>
-  <si>
-    <t>08-7777-88888</t>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>08-0888-01111</t>
+  </si>
+  <si>
+    <t>08-7755-77170</t>
+  </si>
+  <si>
+    <t>4189131-2026131</t>
+  </si>
+  <si>
+    <t>08-0345-00678</t>
   </si>
 </sst>
 </file>
@@ -261,7 +261,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,6 +272,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF88C849"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -310,6 +322,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,7 +681,7 @@
     <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.109375" style="1" bestFit="1" customWidth="1"/>
@@ -728,7 +744,7 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
@@ -799,10 +815,10 @@
       <c r="L2" t="s">
         <v>49</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>70</v>
       </c>
       <c r="O2" t="s">
@@ -811,7 +827,7 @@
       <c r="P2" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="R2" t="s">
@@ -835,74 +851,67 @@
       <c r="Z2"/>
       <c r="AA2"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>126</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>3968</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -939,10 +948,10 @@
       <c r="L4" t="s">
         <v>49</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>72</v>
       </c>
       <c r="O4" t="s">
@@ -951,7 +960,7 @@
       <c r="P4" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="R4" t="s">
@@ -1010,10 +1019,10 @@
       <c r="L5" t="s">
         <v>49</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="4" t="s">
         <v>73</v>
       </c>
       <c r="O5" t="s">
@@ -1022,7 +1031,7 @@
       <c r="P5" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>61</v>
       </c>
       <c r="R5" t="s">

--- a/importaciones/carga masiva reclamo fraude.xlsx
+++ b/importaciones/carga masiva reclamo fraude.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB96800-CD88-4929-AD66-E21825A5DC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7374B3A5-7CBF-4067-970A-CA9BB068AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>cob_110</t>
   </si>
   <si>
-    <t>CL-EVR-RD</t>
-  </si>
-  <si>
     <t>20/09/2026 10:30</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>40</t>
   </si>
   <si>
-    <t>Generales</t>
-  </si>
-  <si>
     <t>15/09/2026</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>313</t>
   </si>
   <si>
@@ -238,10 +229,19 @@
     <t>08-7755-77170</t>
   </si>
   <si>
-    <t>4189131-2026131</t>
-  </si>
-  <si>
     <t>08-0345-00678</t>
+  </si>
+  <si>
+    <t>CL-EV-RD2</t>
+  </si>
+  <si>
+    <t>Fraude en Tarjeta de crédito Visa</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>88-8888-88888</t>
   </si>
 </sst>
 </file>
@@ -314,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -326,6 +326,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,72 +781,72 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="69" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>126</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
       </c>
       <c r="K2">
         <v>3968</v>
       </c>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>38</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>40</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>41</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
       </c>
       <c r="W2"/>
       <c r="X2"/>
@@ -851,66 +854,66 @@
       <c r="Z2"/>
       <c r="AA2"/>
     </row>
-    <row r="3" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="4" customFormat="1" ht="69" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>126</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="K3" s="4">
         <v>3968</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="O3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="V3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
@@ -920,63 +923,63 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
         <v>57</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>58</v>
-      </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" t="s">
-        <v>60</v>
       </c>
       <c r="J4"/>
       <c r="K4">
         <v>3968</v>
       </c>
       <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" t="s">
-        <v>51</v>
-      </c>
       <c r="Q4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" t="s">
         <v>61</v>
       </c>
-      <c r="R4" t="s">
-        <v>62</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>63</v>
-      </c>
       <c r="V4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W4"/>
       <c r="X4"/>
@@ -991,63 +994,63 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
+      <c r="C5" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J5"/>
       <c r="K5">
         <v>3968</v>
       </c>
       <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="O5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" t="s">
-        <v>51</v>
-      </c>
       <c r="Q5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" t="s">
+        <v>60</v>
+      </c>
+      <c r="S5" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" t="s">
         <v>61</v>
       </c>
-      <c r="R5" t="s">
-        <v>62</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" t="s">
-        <v>63</v>
-      </c>
       <c r="V5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W5"/>
       <c r="X5"/>
